--- a/Quantum Threat Modeling for Maritime Critical Infrastructure.xlsx
+++ b/Quantum Threat Modeling for Maritime Critical Infrastructure.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Adhithya\Vit Ap\6th Sem\Cryptology\Assignment\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bd451de075006dfc/Documents/GitHub/Quantum-Threat-Modelling-For-Maritime-Critical-Infrastructure/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{635F56B7-1639-4BBA-9DA7-CBD2B6894331}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{635F56B7-1639-4BBA-9DA7-CBD2B6894331}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D9362D5-2919-49C7-A868-17064931FBB6}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="7. Summary Dashboard" sheetId="1" r:id="rId1"/>
@@ -1459,56 +1459,56 @@
     <xf numFmtId="0" fontId="29" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="19" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -5243,42 +5243,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="38" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="97" t="s">
+      <c r="A1" s="81" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="84"/>
-      <c r="C1" s="84"/>
-      <c r="D1" s="84"/>
-      <c r="E1" s="84"/>
-      <c r="F1" s="84"/>
-      <c r="G1" s="84"/>
-      <c r="H1" s="84"/>
-      <c r="I1" s="84"/>
-      <c r="J1" s="84"/>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="82"/>
+      <c r="F1" s="82"/>
+      <c r="G1" s="82"/>
+      <c r="H1" s="82"/>
+      <c r="I1" s="82"/>
+      <c r="J1" s="82"/>
     </row>
     <row r="3" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="94" t="s">
+      <c r="B3" s="102" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="85" t="s">
+      <c r="C3" s="97" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="85" t="s">
+      <c r="D3" s="97" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="93" t="s">
+      <c r="E3" s="101" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="99" t="s">
+      <c r="F3" s="85" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="99" t="s">
+      <c r="G3" s="85" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="88" t="s">
+      <c r="H3" s="99" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="102" t="s">
+      <c r="I3" s="88" t="s">
         <v>8</v>
       </c>
     </row>
@@ -5286,147 +5286,138 @@
       <c r="B4" s="92" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="82" t="s">
+      <c r="C4" s="83" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="82" t="s">
+      <c r="D4" s="83" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="98" t="s">
+      <c r="E4" s="84" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="86" t="s">
+      <c r="F4" s="93" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="86" t="s">
+      <c r="G4" s="93" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="95" t="s">
+      <c r="H4" s="94" t="s">
         <v>15</v>
       </c>
-      <c r="I4" s="87" t="s">
+      <c r="I4" s="98" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="89"/>
+      <c r="B5" s="100"/>
       <c r="C5" s="90"/>
       <c r="D5" s="90"/>
-      <c r="E5" s="96"/>
-      <c r="F5" s="101"/>
-      <c r="G5" s="101"/>
+      <c r="E5" s="95"/>
+      <c r="F5" s="87"/>
+      <c r="G5" s="87"/>
       <c r="H5" s="91"/>
-      <c r="I5" s="81"/>
+      <c r="I5" s="96"/>
     </row>
     <row r="7" spans="1:10" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="100" t="s">
+      <c r="A7" s="86" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="84"/>
-      <c r="C7" s="84"/>
-      <c r="D7" s="84"/>
-      <c r="E7" s="84"/>
-      <c r="F7" s="84"/>
-      <c r="G7" s="84"/>
-      <c r="H7" s="84"/>
-      <c r="I7" s="84"/>
-      <c r="J7" s="84"/>
+      <c r="B7" s="82"/>
+      <c r="C7" s="82"/>
+      <c r="D7" s="82"/>
+      <c r="E7" s="82"/>
+      <c r="F7" s="82"/>
+      <c r="G7" s="82"/>
+      <c r="H7" s="82"/>
+      <c r="I7" s="82"/>
+      <c r="J7" s="82"/>
     </row>
     <row r="8" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="83" t="s">
+      <c r="A8" s="89" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="84"/>
-      <c r="C8" s="84"/>
-      <c r="D8" s="84"/>
-      <c r="E8" s="84"/>
-      <c r="F8" s="84"/>
-      <c r="G8" s="84"/>
-      <c r="H8" s="84"/>
-      <c r="I8" s="84"/>
-      <c r="J8" s="84"/>
+      <c r="B8" s="82"/>
+      <c r="C8" s="82"/>
+      <c r="D8" s="82"/>
+      <c r="E8" s="82"/>
+      <c r="F8" s="82"/>
+      <c r="G8" s="82"/>
+      <c r="H8" s="82"/>
+      <c r="I8" s="82"/>
+      <c r="J8" s="82"/>
     </row>
     <row r="9" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="83" t="s">
+      <c r="A9" s="89" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="84"/>
-      <c r="C9" s="84"/>
-      <c r="D9" s="84"/>
-      <c r="E9" s="84"/>
-      <c r="F9" s="84"/>
-      <c r="G9" s="84"/>
-      <c r="H9" s="84"/>
-      <c r="I9" s="84"/>
-      <c r="J9" s="84"/>
+      <c r="B9" s="82"/>
+      <c r="C9" s="82"/>
+      <c r="D9" s="82"/>
+      <c r="E9" s="82"/>
+      <c r="F9" s="82"/>
+      <c r="G9" s="82"/>
+      <c r="H9" s="82"/>
+      <c r="I9" s="82"/>
+      <c r="J9" s="82"/>
     </row>
     <row r="10" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="83" t="s">
+      <c r="A10" s="89" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="84"/>
-      <c r="C10" s="84"/>
-      <c r="D10" s="84"/>
-      <c r="E10" s="84"/>
-      <c r="F10" s="84"/>
-      <c r="G10" s="84"/>
-      <c r="H10" s="84"/>
-      <c r="I10" s="84"/>
-      <c r="J10" s="84"/>
+      <c r="B10" s="82"/>
+      <c r="C10" s="82"/>
+      <c r="D10" s="82"/>
+      <c r="E10" s="82"/>
+      <c r="F10" s="82"/>
+      <c r="G10" s="82"/>
+      <c r="H10" s="82"/>
+      <c r="I10" s="82"/>
+      <c r="J10" s="82"/>
     </row>
     <row r="11" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="83" t="s">
+      <c r="A11" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="84"/>
-      <c r="C11" s="84"/>
-      <c r="D11" s="84"/>
-      <c r="E11" s="84"/>
-      <c r="F11" s="84"/>
-      <c r="G11" s="84"/>
-      <c r="H11" s="84"/>
-      <c r="I11" s="84"/>
-      <c r="J11" s="84"/>
+      <c r="B11" s="82"/>
+      <c r="C11" s="82"/>
+      <c r="D11" s="82"/>
+      <c r="E11" s="82"/>
+      <c r="F11" s="82"/>
+      <c r="G11" s="82"/>
+      <c r="H11" s="82"/>
+      <c r="I11" s="82"/>
+      <c r="J11" s="82"/>
     </row>
     <row r="12" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="83" t="s">
+      <c r="A12" s="89" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="84"/>
-      <c r="C12" s="84"/>
-      <c r="D12" s="84"/>
-      <c r="E12" s="84"/>
-      <c r="F12" s="84"/>
-      <c r="G12" s="84"/>
-      <c r="H12" s="84"/>
-      <c r="I12" s="84"/>
-      <c r="J12" s="84"/>
+      <c r="B12" s="82"/>
+      <c r="C12" s="82"/>
+      <c r="D12" s="82"/>
+      <c r="E12" s="82"/>
+      <c r="F12" s="82"/>
+      <c r="G12" s="82"/>
+      <c r="H12" s="82"/>
+      <c r="I12" s="82"/>
+      <c r="J12" s="82"/>
     </row>
     <row r="13" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="83" t="s">
+      <c r="A13" s="89" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="84"/>
-      <c r="C13" s="84"/>
-      <c r="D13" s="84"/>
-      <c r="E13" s="84"/>
-      <c r="F13" s="84"/>
-      <c r="G13" s="84"/>
-      <c r="H13" s="84"/>
-      <c r="I13" s="84"/>
-      <c r="J13" s="84"/>
+      <c r="B13" s="82"/>
+      <c r="C13" s="82"/>
+      <c r="D13" s="82"/>
+      <c r="E13" s="82"/>
+      <c r="F13" s="82"/>
+      <c r="G13" s="82"/>
+      <c r="H13" s="82"/>
+      <c r="I13" s="82"/>
+      <c r="J13" s="82"/>
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="C4"/>
-    <mergeCell ref="E4"/>
-    <mergeCell ref="F3"/>
-    <mergeCell ref="A7:J7"/>
-    <mergeCell ref="F5"/>
-    <mergeCell ref="G3"/>
-    <mergeCell ref="I3"/>
-    <mergeCell ref="G5"/>
     <mergeCell ref="A10:J10"/>
     <mergeCell ref="D5"/>
     <mergeCell ref="A13:J13"/>
@@ -5442,8 +5433,17 @@
     <mergeCell ref="I5"/>
     <mergeCell ref="D4"/>
     <mergeCell ref="A8:J8"/>
+    <mergeCell ref="G4"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="C4"/>
+    <mergeCell ref="E4"/>
+    <mergeCell ref="F3"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="F5"/>
+    <mergeCell ref="G3"/>
+    <mergeCell ref="I3"/>
+    <mergeCell ref="G5"/>
     <mergeCell ref="D3"/>
-    <mergeCell ref="G4"/>
     <mergeCell ref="I4"/>
     <mergeCell ref="H3"/>
     <mergeCell ref="B5"/>
@@ -5473,25 +5473,25 @@
       <c r="A1" s="104" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="84"/>
-      <c r="C1" s="84"/>
-      <c r="D1" s="84"/>
-      <c r="E1" s="84"/>
-      <c r="F1" s="84"/>
-      <c r="G1" s="84"/>
-      <c r="H1" s="84"/>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="82"/>
+      <c r="F1" s="82"/>
+      <c r="G1" s="82"/>
+      <c r="H1" s="82"/>
     </row>
     <row r="2" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="103" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="84"/>
-      <c r="C2" s="84"/>
-      <c r="D2" s="84"/>
-      <c r="E2" s="84"/>
-      <c r="F2" s="84"/>
-      <c r="G2" s="84"/>
-      <c r="H2" s="84"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="82"/>
+      <c r="D2" s="82"/>
+      <c r="E2" s="82"/>
+      <c r="F2" s="82"/>
+      <c r="G2" s="82"/>
+      <c r="H2" s="82"/>
     </row>
     <row r="4" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
@@ -5823,27 +5823,27 @@
       <c r="A1" s="105" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="84"/>
-      <c r="C1" s="84"/>
-      <c r="D1" s="84"/>
-      <c r="E1" s="84"/>
-      <c r="F1" s="84"/>
-      <c r="G1" s="84"/>
-      <c r="H1" s="84"/>
-      <c r="I1" s="84"/>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="82"/>
+      <c r="F1" s="82"/>
+      <c r="G1" s="82"/>
+      <c r="H1" s="82"/>
+      <c r="I1" s="82"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="103" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="84"/>
-      <c r="C2" s="84"/>
-      <c r="D2" s="84"/>
-      <c r="E2" s="84"/>
-      <c r="F2" s="84"/>
-      <c r="G2" s="84"/>
-      <c r="H2" s="84"/>
-      <c r="I2" s="84"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="82"/>
+      <c r="D2" s="82"/>
+      <c r="E2" s="82"/>
+      <c r="F2" s="82"/>
+      <c r="G2" s="82"/>
+      <c r="H2" s="82"/>
+      <c r="I2" s="82"/>
     </row>
     <row r="4" spans="1:9" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="10" t="s">
@@ -6322,23 +6322,23 @@
       <c r="A1" s="106" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="84"/>
-      <c r="C1" s="84"/>
-      <c r="D1" s="84"/>
-      <c r="E1" s="84"/>
-      <c r="F1" s="84"/>
-      <c r="G1" s="84"/>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="82"/>
+      <c r="F1" s="82"/>
+      <c r="G1" s="82"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="103" t="s">
         <v>89</v>
       </c>
-      <c r="B2" s="84"/>
-      <c r="C2" s="84"/>
-      <c r="D2" s="84"/>
-      <c r="E2" s="84"/>
-      <c r="F2" s="84"/>
-      <c r="G2" s="84"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="82"/>
+      <c r="D2" s="82"/>
+      <c r="E2" s="82"/>
+      <c r="F2" s="82"/>
+      <c r="G2" s="82"/>
     </row>
     <row r="4" spans="1:10" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="31" t="s">
@@ -6686,21 +6686,21 @@
       <c r="A1" s="109" t="s">
         <v>120</v>
       </c>
-      <c r="B1" s="84"/>
-      <c r="C1" s="84"/>
-      <c r="D1" s="84"/>
-      <c r="E1" s="84"/>
-      <c r="F1" s="84"/>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="82"/>
+      <c r="F1" s="82"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="103" t="s">
         <v>121</v>
       </c>
-      <c r="B2" s="84"/>
-      <c r="C2" s="84"/>
-      <c r="D2" s="84"/>
-      <c r="E2" s="84"/>
-      <c r="F2" s="84"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="82"/>
+      <c r="D2" s="82"/>
+      <c r="E2" s="82"/>
+      <c r="F2" s="82"/>
     </row>
     <row r="4" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="42" t="s">
@@ -6886,22 +6886,22 @@
       <c r="A13" s="107" t="s">
         <v>138</v>
       </c>
-      <c r="B13" s="84"/>
-      <c r="C13" s="84"/>
-      <c r="D13" s="84"/>
-      <c r="E13" s="84"/>
-      <c r="F13" s="84"/>
+      <c r="B13" s="82"/>
+      <c r="C13" s="82"/>
+      <c r="D13" s="82"/>
+      <c r="E13" s="82"/>
+      <c r="F13" s="82"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="108">
         <f>SUMIF(D5:D12,"&lt;80",E5:E12)/SUM(E5:E12)</f>
         <v>0.46675900277008309</v>
       </c>
-      <c r="B14" s="84"/>
-      <c r="C14" s="84"/>
-      <c r="D14" s="84"/>
-      <c r="E14" s="84"/>
-      <c r="F14" s="84"/>
+      <c r="B14" s="82"/>
+      <c r="C14" s="82"/>
+      <c r="D14" s="82"/>
+      <c r="E14" s="82"/>
+      <c r="F14" s="82"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -6933,25 +6933,25 @@
       <c r="A1" s="110" t="s">
         <v>139</v>
       </c>
-      <c r="B1" s="84"/>
-      <c r="C1" s="84"/>
-      <c r="D1" s="84"/>
-      <c r="E1" s="84"/>
-      <c r="F1" s="84"/>
-      <c r="G1" s="84"/>
-      <c r="H1" s="84"/>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="82"/>
+      <c r="F1" s="82"/>
+      <c r="G1" s="82"/>
+      <c r="H1" s="82"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="103" t="s">
         <v>140</v>
       </c>
-      <c r="B2" s="84"/>
-      <c r="C2" s="84"/>
-      <c r="D2" s="84"/>
-      <c r="E2" s="84"/>
-      <c r="F2" s="84"/>
-      <c r="G2" s="84"/>
-      <c r="H2" s="84"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="82"/>
+      <c r="D2" s="82"/>
+      <c r="E2" s="82"/>
+      <c r="F2" s="82"/>
+      <c r="G2" s="82"/>
+      <c r="H2" s="82"/>
     </row>
     <row r="4" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="54" t="s">
@@ -7168,23 +7168,23 @@
       <c r="A1" s="104" t="s">
         <v>161</v>
       </c>
-      <c r="B1" s="84"/>
-      <c r="C1" s="84"/>
-      <c r="D1" s="84"/>
-      <c r="E1" s="84"/>
-      <c r="F1" s="84"/>
-      <c r="G1" s="84"/>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="82"/>
+      <c r="F1" s="82"/>
+      <c r="G1" s="82"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="103" t="s">
         <v>162</v>
       </c>
-      <c r="B2" s="84"/>
-      <c r="C2" s="84"/>
-      <c r="D2" s="84"/>
-      <c r="E2" s="84"/>
-      <c r="F2" s="84"/>
-      <c r="G2" s="84"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="82"/>
+      <c r="D2" s="82"/>
+      <c r="E2" s="82"/>
+      <c r="F2" s="82"/>
+      <c r="G2" s="82"/>
     </row>
     <row r="4" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="63" t="s">
@@ -7477,23 +7477,23 @@
       <c r="A1" s="112" t="s">
         <v>196</v>
       </c>
-      <c r="B1" s="84"/>
-      <c r="C1" s="84"/>
-      <c r="D1" s="84"/>
-      <c r="E1" s="84"/>
-      <c r="F1" s="84"/>
-      <c r="G1" s="84"/>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="82"/>
+      <c r="F1" s="82"/>
+      <c r="G1" s="82"/>
     </row>
     <row r="2" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="111" t="s">
         <v>197</v>
       </c>
-      <c r="B2" s="84"/>
-      <c r="C2" s="84"/>
-      <c r="D2" s="84"/>
-      <c r="E2" s="84"/>
-      <c r="F2" s="84"/>
-      <c r="G2" s="84"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="82"/>
+      <c r="D2" s="82"/>
+      <c r="E2" s="82"/>
+      <c r="F2" s="82"/>
+      <c r="G2" s="82"/>
     </row>
     <row r="4" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="70" t="s">
@@ -7959,12 +7959,12 @@
       <c r="A25" s="113" t="s">
         <v>289</v>
       </c>
-      <c r="B25" s="84"/>
-      <c r="C25" s="84"/>
-      <c r="D25" s="84"/>
-      <c r="E25" s="84"/>
-      <c r="F25" s="84"/>
-      <c r="G25" s="84"/>
+      <c r="B25" s="82"/>
+      <c r="C25" s="82"/>
+      <c r="D25" s="82"/>
+      <c r="E25" s="82"/>
+      <c r="F25" s="82"/>
+      <c r="G25" s="82"/>
     </row>
   </sheetData>
   <mergeCells count="3">
